--- a/Prueba1/Situacion4 xlsx.xlsx
+++ b/Prueba1/Situacion4 xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\Prueba\Prueba1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F5D9C8-D1B7-4F1C-93D2-805D4ED904CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF52FB2-297A-486A-B876-CE5EF4847F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{33CB6783-46B9-4933-92AD-501A277555F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="9" activeTab="14" xr2:uid="{33CB6783-46B9-4933-92AD-501A277555F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Situacion 4" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,17 @@
     <sheet name="Estudios Geotecnicos" sheetId="4" r:id="rId4"/>
     <sheet name="Asentamientos Criticos" sheetId="5" r:id="rId5"/>
     <sheet name="Situacion 9" sheetId="6" r:id="rId6"/>
-    <sheet name="Monitoreo Situacion 9" sheetId="7" r:id="rId7"/>
-    <sheet name="Situacion 10" sheetId="8" r:id="rId8"/>
-    <sheet name="Monitoreo Situacion 10" sheetId="9" r:id="rId9"/>
+    <sheet name="Situacion 1" sheetId="10" r:id="rId7"/>
+    <sheet name="View Situacion 1" sheetId="11" r:id="rId8"/>
+    <sheet name=" S2 Estado Estructural" sheetId="12" r:id="rId9"/>
+    <sheet name="S2 Asentamientos Criticos" sheetId="13" r:id="rId10"/>
+    <sheet name="Vista Situacion 2" sheetId="14" r:id="rId11"/>
+    <sheet name="Monitoreo Situacion 9" sheetId="7" r:id="rId12"/>
+    <sheet name="Situacion 3 Inventario" sheetId="15" r:id="rId13"/>
+    <sheet name="Situacion 3 Alertas Stock" sheetId="16" r:id="rId14"/>
+    <sheet name="Trigger Situacion 3" sheetId="17" r:id="rId15"/>
+    <sheet name="Situacion 10" sheetId="8" r:id="rId16"/>
+    <sheet name="Monitoreo Situacion 10" sheetId="9" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="143">
   <si>
     <t>id_asistencia</t>
   </si>
@@ -350,13 +358,139 @@
   </si>
   <si>
     <t>Recalcular cargas estructurales</t>
+  </si>
+  <si>
+    <t>id_alerta</t>
+  </si>
+  <si>
+    <t>id_proyecto</t>
+  </si>
+  <si>
+    <t>tipo_alerta</t>
+  </si>
+  <si>
+    <t>nivel_alerta</t>
+  </si>
+  <si>
+    <t>fecha_alerta</t>
+  </si>
+  <si>
+    <t>Seguridad</t>
+  </si>
+  <si>
+    <t>Acceso restringido bloqueado parcialmente</t>
+  </si>
+  <si>
+    <t>Asentamiento</t>
+  </si>
+  <si>
+    <t>Asentamiento fuera del rango permitido</t>
+  </si>
+  <si>
+    <t>Crítica</t>
+  </si>
+  <si>
+    <t>Clima</t>
+  </si>
+  <si>
+    <t>Lluvias intensas previstas en la zona</t>
+  </si>
+  <si>
+    <t>Trabajador sin casco detectado</t>
+  </si>
+  <si>
+    <t>id_esfuerzo</t>
+  </si>
+  <si>
+    <t>elemento</t>
+  </si>
+  <si>
+    <t>flexion</t>
+  </si>
+  <si>
+    <t>cortante</t>
+  </si>
+  <si>
+    <t>torsion</t>
+  </si>
+  <si>
+    <t>carga_viva</t>
+  </si>
+  <si>
+    <t>carga_muerta</t>
+  </si>
+  <si>
+    <t>Viga</t>
+  </si>
+  <si>
+    <t>Columna</t>
+  </si>
+  <si>
+    <t>Losa</t>
+  </si>
+  <si>
+    <t>Monitorear</t>
+  </si>
+  <si>
+    <t>Estable</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>id_inventario</t>
+  </si>
+  <si>
+    <t>stock_actual_kg</t>
+  </si>
+  <si>
+    <t>stock_minimo_kg</t>
+  </si>
+  <si>
+    <t>fecha_actualizacion</t>
+  </si>
+  <si>
+    <t>proyecto</t>
+  </si>
+  <si>
+    <t>Sistema</t>
+  </si>
+  <si>
+    <t>Error de sincronización de registros</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Inventario</t>
+  </si>
+  <si>
+    <t>Hidráulica</t>
+  </si>
+  <si>
+    <t>Caudal excede el límite proyectado</t>
+  </si>
+  <si>
+    <t>Estructural</t>
+  </si>
+  <si>
+    <t>Nivel de torsión elevado en viga principal</t>
+  </si>
+  <si>
+    <t>Excavadora requiere mantenimiento preventivo</t>
+  </si>
+  <si>
+    <t>Stock bajo</t>
+  </si>
+  <si>
+    <t>El cemento está por debajo del stock mínimo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -724,9 +858,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437E8B53-E4A4-4739-ADC5-1A5E4AA263F1}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -746,7 +880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -766,7 +900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -786,7 +920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -806,7 +940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -826,7 +960,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -846,7 +980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -866,7 +1000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -886,7 +1020,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -906,7 +1040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -926,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -946,7 +1080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -966,7 +1100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -986,7 +1120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1006,7 +1140,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1026,7 +1160,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1044,6 +1178,1332 @@
       </c>
       <c r="F16">
         <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317F82B8-2855-4D35-A066-37670C6614D2}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46039</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1">
+        <v>46038</v>
+      </c>
+      <c r="E3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46037</v>
+      </c>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46036</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46035</v>
+      </c>
+      <c r="E6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46034</v>
+      </c>
+      <c r="E7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46033</v>
+      </c>
+      <c r="E8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46032</v>
+      </c>
+      <c r="E9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1">
+        <v>46031</v>
+      </c>
+      <c r="E10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9140D80E-D6EF-466F-8215-DFF6F53930E9}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46143.427083333336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46144.270833333336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46146.465277777781</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46147.642361111109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8529395-B1C9-4F0C-A9C0-1FE085469671}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2">
+        <v>200</v>
+      </c>
+      <c r="E2">
+        <v>6500</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3">
+        <v>200</v>
+      </c>
+      <c r="E3">
+        <v>9000</v>
+      </c>
+      <c r="F3" s="1">
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>2200</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5">
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>1800</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6">
+        <v>240</v>
+      </c>
+      <c r="E6">
+        <v>7800</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7">
+        <v>250</v>
+      </c>
+      <c r="E7">
+        <v>11250</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8">
+        <v>625</v>
+      </c>
+      <c r="E8">
+        <v>750</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46152</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ECBF8F3-2481-4432-B8A4-93B486AB1063}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>5000</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3500</v>
+      </c>
+      <c r="D3">
+        <v>800</v>
+      </c>
+      <c r="E3" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>2200</v>
+      </c>
+      <c r="D4">
+        <v>500</v>
+      </c>
+      <c r="E4" s="1">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1800</v>
+      </c>
+      <c r="D5">
+        <v>400</v>
+      </c>
+      <c r="E5" s="1">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1200</v>
+      </c>
+      <c r="D6">
+        <v>300</v>
+      </c>
+      <c r="E6" s="1">
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>800</v>
+      </c>
+      <c r="D7">
+        <v>250</v>
+      </c>
+      <c r="E7" s="1">
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>950</v>
+      </c>
+      <c r="D8">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="1">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>700</v>
+      </c>
+      <c r="D9">
+        <v>800</v>
+      </c>
+      <c r="E9" s="1">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>450</v>
+      </c>
+      <c r="D10">
+        <v>500</v>
+      </c>
+      <c r="E10" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>5200</v>
+      </c>
+      <c r="D11">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="1">
+        <v>46149</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E13B21-9CCB-4C43-943A-E7A1D482A8B5}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>950</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>700</v>
+      </c>
+      <c r="D3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>450</v>
+      </c>
+      <c r="D4">
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD8EC64-92ED-4878-9302-04C382B56F83}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46148.694444444445</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46148.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46147.642361111109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46147.326388888891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" s="2">
+        <v>46146.465277777781</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="2">
+        <v>46145.614583333336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="2">
+        <v>46145.388888888891</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46144.270833333336</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="2">
+        <v>46143.427083333336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="2">
+        <v>46143.333333333336</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5413FD4-AB17-4517-B031-0DAF9FD235EB}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB0BB790-246D-4277-91F6-24CBD8AC27C5}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1054,9 +2514,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5F51FE-EAA8-45FD-B3B6-9F71812470F8}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -1073,7 +2533,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1090,7 +2550,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1107,7 +2567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1124,7 +2584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1141,7 +2601,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1158,7 +2618,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1175,7 +2635,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1192,7 +2652,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1209,7 +2669,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1226,7 +2686,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1251,9 +2711,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADE61367-0264-4F7A-B522-36EBFFD1DC7D}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -1270,7 +2730,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>4</v>
       </c>
@@ -1287,7 +2747,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>8</v>
       </c>
@@ -1312,9 +2772,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C69A98FE-C3CC-4211-861A-1DE083959A89}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>47</v>
       </c>
@@ -1334,7 +2794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>5</v>
       </c>
@@ -1354,7 +2814,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>4</v>
       </c>
@@ -1374,7 +2834,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1394,7 +2854,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1414,7 +2874,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1442,9 +2902,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E5171B1-49DE-4C6D-B2FA-0641D5A5F488}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>59</v>
       </c>
@@ -1458,7 +2918,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>14</v>
       </c>
@@ -1472,7 +2932,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>15</v>
       </c>
@@ -1486,7 +2946,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>16</v>
       </c>
@@ -1500,7 +2960,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>17</v>
       </c>
@@ -1522,9 +2982,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E60B3FA-5494-488B-ACF2-6AC5C531B9A9}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>65</v>
       </c>
@@ -1544,7 +3004,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1564,7 +3024,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1584,7 +3044,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1604,7 +3064,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1624,7 +3084,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1644,7 +3104,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1664,7 +3124,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1690,168 +3150,108 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8529395-B1C9-4F0C-A9C0-1FE085469671}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16540AA0-FC27-4994-B65F-FC3EBAFAC0C5}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2">
-        <v>200</v>
-      </c>
-      <c r="E2">
-        <v>6500</v>
-      </c>
-      <c r="F2" s="1">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="D2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46147.642361111109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
+        <v>6</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
       <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3">
-        <v>200</v>
-      </c>
-      <c r="E3">
-        <v>9000</v>
-      </c>
-      <c r="F3" s="1">
-        <v>46145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="D3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46146.465277777781</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>74</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4">
-        <v>40</v>
-      </c>
-      <c r="E4">
-        <v>2200</v>
-      </c>
-      <c r="F4" s="1">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="D4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46144.270833333336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5">
-        <v>30</v>
-      </c>
-      <c r="E5">
-        <v>1800</v>
-      </c>
-      <c r="F5" s="1">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6">
-        <v>240</v>
-      </c>
-      <c r="E6">
-        <v>7800</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7">
-        <v>250</v>
-      </c>
-      <c r="E7">
-        <v>11250</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8">
-        <v>625</v>
-      </c>
-      <c r="E8">
-        <v>750</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46152</v>
+        <v>106</v>
+      </c>
+      <c r="D5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46143.427083333336</v>
       </c>
     </row>
   </sheetData>
@@ -1860,168 +3260,108 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5413FD4-AB17-4517-B031-0DAF9FD235EB}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69175C44-2BB1-4180-B708-7EBF9AD98C34}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" t="s">
-        <v>80</v>
-      </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="F1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>83</v>
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46143.427083333336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" t="s">
         <v>84</v>
       </c>
-      <c r="D2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="F3" s="2">
+        <v>46144.270833333336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46146.465277777781</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" t="s">
         <v>88</v>
       </c>
-      <c r="D3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" t="s">
-        <v>100</v>
+      <c r="F5" s="2">
+        <v>46147.642361111109</v>
       </c>
     </row>
   </sheetData>
@@ -2030,168 +3370,1334 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB0BB790-246D-4277-91F6-24CBD8AC27C5}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0A93352-5A1C-4C13-B0AB-61FC849D24C8}">
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>50</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2">
+        <v>88</v>
+      </c>
+      <c r="E2">
+        <v>39</v>
+      </c>
+      <c r="F2">
+        <v>16</v>
+      </c>
+      <c r="G2">
+        <v>69</v>
+      </c>
+      <c r="H2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>49</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3">
+        <v>108</v>
+      </c>
+      <c r="E3">
+        <v>37</v>
+      </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>68</v>
+      </c>
+      <c r="H3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>48</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4">
+        <v>107</v>
+      </c>
+      <c r="E4">
+        <v>36</v>
+      </c>
+      <c r="F4">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>67</v>
+      </c>
+      <c r="H4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>47</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5">
+        <v>106</v>
+      </c>
+      <c r="E5">
+        <v>35</v>
+      </c>
+      <c r="F5">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>66</v>
+      </c>
+      <c r="H5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>46</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6">
+        <v>105</v>
+      </c>
+      <c r="E6">
+        <v>34</v>
+      </c>
+      <c r="F6">
+        <v>14</v>
+      </c>
+      <c r="G6">
+        <v>65</v>
+      </c>
+      <c r="H6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>45</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7">
+        <v>104</v>
+      </c>
+      <c r="E7">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>64</v>
+      </c>
+      <c r="H7">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>44</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8">
+        <v>103</v>
+      </c>
+      <c r="E8">
+        <v>32</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>63</v>
+      </c>
+      <c r="H8">
         <v>78</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>43</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9">
+        <v>102</v>
+      </c>
+      <c r="E9">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>62</v>
+      </c>
+      <c r="H9">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>42</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10">
+        <v>101</v>
+      </c>
+      <c r="E10">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>61</v>
+      </c>
+      <c r="H10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>41</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>39</v>
+      </c>
+      <c r="F11">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>60</v>
+      </c>
+      <c r="H11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>40</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12">
+        <v>99</v>
+      </c>
+      <c r="E12">
+        <v>38</v>
+      </c>
+      <c r="F12">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>59</v>
+      </c>
+      <c r="H12">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>39</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13">
+        <v>98</v>
+      </c>
+      <c r="E13">
+        <v>37</v>
+      </c>
+      <c r="F13">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>58</v>
+      </c>
+      <c r="H13">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>38</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14">
+        <v>97</v>
+      </c>
+      <c r="E14">
+        <v>36</v>
+      </c>
+      <c r="F14">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>57</v>
+      </c>
+      <c r="H14">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>37</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15">
+        <v>96</v>
+      </c>
+      <c r="E15">
+        <v>35</v>
+      </c>
+      <c r="F15">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>56</v>
+      </c>
+      <c r="H15">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>36</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16">
+        <v>95</v>
+      </c>
+      <c r="E16">
+        <v>34</v>
+      </c>
+      <c r="F16">
+        <v>14</v>
+      </c>
+      <c r="G16">
+        <v>55</v>
+      </c>
+      <c r="H16">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
+        <v>35</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17">
+        <v>94</v>
+      </c>
+      <c r="E17">
+        <v>33</v>
+      </c>
+      <c r="F17">
         <v>13</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G17">
+        <v>54</v>
+      </c>
+      <c r="H17">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18">
+        <v>34</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18">
+        <v>93</v>
+      </c>
+      <c r="E18">
+        <v>32</v>
+      </c>
+      <c r="F18">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>53</v>
+      </c>
+      <c r="H18">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
+        <v>33</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19">
+        <v>92</v>
+      </c>
+      <c r="E19">
+        <v>31</v>
+      </c>
+      <c r="F19">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>52</v>
+      </c>
+      <c r="H19">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20">
+        <v>32</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20">
+        <v>91</v>
+      </c>
+      <c r="E20">
+        <v>30</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>51</v>
+      </c>
+      <c r="H20">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21">
+        <v>31</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21">
+        <v>90</v>
+      </c>
+      <c r="E21">
+        <v>39</v>
+      </c>
+      <c r="F21">
+        <v>16</v>
+      </c>
+      <c r="G21">
+        <v>50</v>
+      </c>
+      <c r="H21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22">
+        <v>30</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22">
+        <v>89</v>
+      </c>
+      <c r="E22">
+        <v>38</v>
+      </c>
+      <c r="F22">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>49</v>
+      </c>
+      <c r="H22">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23">
+        <v>29</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23">
+        <v>88</v>
+      </c>
+      <c r="E23">
+        <v>37</v>
+      </c>
+      <c r="F23">
+        <v>14</v>
+      </c>
+      <c r="G23">
+        <v>48</v>
+      </c>
+      <c r="H23">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24">
+        <v>28</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24">
+        <v>87</v>
+      </c>
+      <c r="E24">
+        <v>36</v>
+      </c>
+      <c r="F24">
+        <v>16</v>
+      </c>
+      <c r="G24">
+        <v>47</v>
+      </c>
+      <c r="H24">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25">
+        <v>27</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25">
+        <v>86</v>
+      </c>
+      <c r="E25">
+        <v>35</v>
+      </c>
+      <c r="F25">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>46</v>
+      </c>
+      <c r="H25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26">
+        <v>85</v>
+      </c>
+      <c r="E26">
+        <v>34</v>
+      </c>
+      <c r="F26">
+        <v>14</v>
+      </c>
+      <c r="G26">
+        <v>45</v>
+      </c>
+      <c r="H26">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27">
+        <v>84</v>
+      </c>
+      <c r="E27">
+        <v>33</v>
+      </c>
+      <c r="F27">
+        <v>13</v>
+      </c>
+      <c r="G27">
+        <v>44</v>
+      </c>
+      <c r="H27">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28">
+        <v>83</v>
+      </c>
+      <c r="E28">
+        <v>32</v>
+      </c>
+      <c r="F28">
+        <v>12</v>
+      </c>
+      <c r="G28">
+        <v>43</v>
+      </c>
+      <c r="H28">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>23</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29">
+        <v>82</v>
+      </c>
+      <c r="E29">
+        <v>31</v>
+      </c>
+      <c r="F29">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>42</v>
+      </c>
+      <c r="H29">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>22</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30">
+        <v>81</v>
+      </c>
+      <c r="E30">
+        <v>30</v>
+      </c>
+      <c r="F30">
+        <v>10</v>
+      </c>
+      <c r="G30">
+        <v>41</v>
+      </c>
+      <c r="H30">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31">
+        <v>21</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31">
+        <v>80</v>
+      </c>
+      <c r="E31">
+        <v>39</v>
+      </c>
+      <c r="F31">
+        <v>16</v>
+      </c>
+      <c r="G31">
+        <v>40</v>
+      </c>
+      <c r="H31">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32">
+        <v>20</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32">
         <v>79</v>
       </c>
-      <c r="D1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="E32">
+        <v>38</v>
+      </c>
+      <c r="F32">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>39</v>
+      </c>
+      <c r="H32">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33">
+        <v>19</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33">
+        <v>78</v>
+      </c>
+      <c r="E33">
+        <v>37</v>
+      </c>
+      <c r="F33">
+        <v>14</v>
+      </c>
+      <c r="G33">
+        <v>38</v>
+      </c>
+      <c r="H33">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34">
+        <v>18</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34">
+        <v>77</v>
+      </c>
+      <c r="E34">
+        <v>36</v>
+      </c>
+      <c r="F34">
+        <v>13</v>
+      </c>
+      <c r="G34">
+        <v>37</v>
+      </c>
+      <c r="H34">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35">
+        <v>17</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35">
+        <v>76</v>
+      </c>
+      <c r="E35">
+        <v>35</v>
+      </c>
+      <c r="F35">
+        <v>12</v>
+      </c>
+      <c r="G35">
+        <v>36</v>
+      </c>
+      <c r="H35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36">
+        <v>16</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D36">
+        <v>75</v>
+      </c>
+      <c r="E36">
+        <v>34</v>
+      </c>
+      <c r="F36">
+        <v>14</v>
+      </c>
+      <c r="G36">
+        <v>35</v>
+      </c>
+      <c r="H36">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37">
+        <v>15</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37">
+        <v>74</v>
+      </c>
+      <c r="E37">
+        <v>33</v>
+      </c>
+      <c r="F37">
+        <v>13</v>
+      </c>
+      <c r="G37">
+        <v>34</v>
+      </c>
+      <c r="H37">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38">
+        <v>14</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38">
+        <v>72</v>
+      </c>
+      <c r="E38">
+        <v>32</v>
+      </c>
+      <c r="F38">
+        <v>12</v>
+      </c>
+      <c r="G38">
+        <v>33</v>
+      </c>
+      <c r="H38">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39">
+        <v>13</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39">
+        <v>70</v>
+      </c>
+      <c r="E39">
+        <v>31</v>
+      </c>
+      <c r="F39">
+        <v>11</v>
+      </c>
+      <c r="G39">
+        <v>32</v>
+      </c>
+      <c r="H39">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40">
+        <v>12</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40">
+        <v>69</v>
+      </c>
+      <c r="E40">
+        <v>30</v>
+      </c>
+      <c r="F40">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>31</v>
+      </c>
+      <c r="H40">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41">
+        <v>11</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41">
+        <v>67</v>
+      </c>
+      <c r="E41">
+        <v>29</v>
+      </c>
+      <c r="F41">
+        <v>12</v>
+      </c>
+      <c r="G41">
+        <v>30</v>
+      </c>
+      <c r="H41">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42">
+        <v>10</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42">
+        <v>65</v>
+      </c>
+      <c r="E42">
+        <v>28</v>
+      </c>
+      <c r="F42">
+        <v>11</v>
+      </c>
+      <c r="G42">
+        <v>29</v>
+      </c>
+      <c r="H42">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43">
+        <v>9</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>121</v>
+      </c>
+      <c r="D43">
+        <v>63</v>
+      </c>
+      <c r="E43">
+        <v>27</v>
+      </c>
+      <c r="F43">
+        <v>10</v>
+      </c>
+      <c r="G43">
+        <v>28</v>
+      </c>
+      <c r="H43">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44">
+        <v>8</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>123</v>
+      </c>
+      <c r="D44">
+        <v>60</v>
+      </c>
+      <c r="E44">
+        <v>25</v>
+      </c>
+      <c r="F44">
+        <v>9</v>
+      </c>
+      <c r="G44">
+        <v>27</v>
+      </c>
+      <c r="H44">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45">
+        <v>7</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45">
+        <v>58</v>
+      </c>
+      <c r="E45">
+        <v>24</v>
+      </c>
+      <c r="F45">
+        <v>8</v>
+      </c>
+      <c r="G45">
+        <v>26</v>
+      </c>
+      <c r="H45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46">
+        <v>6</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>121</v>
+      </c>
+      <c r="D46">
+        <v>55</v>
+      </c>
+      <c r="E46">
+        <v>22</v>
+      </c>
+      <c r="F46">
+        <v>7</v>
+      </c>
+      <c r="G46">
+        <v>25</v>
+      </c>
+      <c r="H46">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47">
+        <v>5</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47">
+        <v>49</v>
+      </c>
+      <c r="E47">
+        <v>20</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47">
+        <v>24</v>
+      </c>
+      <c r="H47">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>121</v>
+      </c>
+      <c r="D48">
+        <v>52</v>
+      </c>
+      <c r="E48">
+        <v>21</v>
+      </c>
+      <c r="F48">
+        <v>6</v>
+      </c>
+      <c r="G48">
+        <v>23</v>
+      </c>
+      <c r="H48">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49">
+        <v>3</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>122</v>
+      </c>
+      <c r="D49">
+        <v>50</v>
+      </c>
+      <c r="E49">
+        <v>19</v>
+      </c>
+      <c r="F49">
+        <v>7</v>
+      </c>
+      <c r="G49">
+        <v>22</v>
+      </c>
+      <c r="H49">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50">
+        <v>48</v>
+      </c>
+      <c r="E50">
+        <v>20</v>
+      </c>
+      <c r="F50">
+        <v>6</v>
+      </c>
+      <c r="G50">
+        <v>21</v>
+      </c>
+      <c r="H50">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>121</v>
+      </c>
+      <c r="D51">
+        <v>45</v>
+      </c>
+      <c r="E51">
+        <v>18</v>
+      </c>
+      <c r="F51">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" t="s">
-        <v>100</v>
+      <c r="G51">
+        <v>20</v>
+      </c>
+      <c r="H51">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
